--- a/StructureDefinition-ncpi-participant.xlsx
+++ b/StructureDefinition-ncpi-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T23:53:55+00:00</t>
+    <t>2025-12-03T18:37:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -365,7 +365,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -838,7 +838,7 @@
     <t>The domestic partnership status of a person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
+    <t>http://hl7.org/fhir/ValueSet/marital-status|4.0.1</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -989,7 +989,7 @@
     <t>The nature of the relationship between a patient and a contact person for that patient.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
+    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.0.1</t>
   </si>
   <si>
     <t>code</t>
@@ -1058,7 +1058,7 @@
     <t>Patient.contact.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1182,7 +1182,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1253,7 +1253,7 @@
     <t>Patient.link.other</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1611,7 +1611,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="69.35546875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="44.51171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.33203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-ncpi-participant.xlsx
+++ b/StructureDefinition-ncpi-participant.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2015" uniqueCount="408">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T18:37:31+00:00</t>
+    <t>2025-12-03T22:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NCPI FHIR Working Group (http://example.org/example-publisher, ncpi-fhir-ig@googlegroups.com)</t>
+    <t>NCPI FHIR Working Group (https://www.ncpi-acc.org/about/working-groups, ncpi-fhir-ig@googlegroups.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -559,6 +559,26 @@
   </si>
   <si>
     <t>Age at Last Vital Status Extension</t>
+  </si>
+  <si>
+    <t>Patient.extension:patientKnowledgeSource</t>
+  </si>
+  <si>
+    <t>patientKnowledgeSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://nih-ncpi.github.io/ncpi-fhir-ig-2/StructureDefinition/patient-knowledge-source}
+</t>
+  </si>
+  <si>
+    <t>The source of the knowledge represented by this Patient resource.</t>
+  </si>
+  <si>
+    <t>An extension to record the source of the knowledge in a particular
+`Patient` resource.
+The primary use case is to identify those `Patient` resources
+created via inference in order to support indirect pedigree
+relationships.</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -1583,12 +1603,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO52"/>
+  <dimension ref="A1:AO53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="33.83984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="34.82421875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.83984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.32421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="20.5625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3390,43 +3410,41 @@
         <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="O16" t="s" s="2">
-        <v>178</v>
-      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>20</v>
       </c>
@@ -3474,7 +3492,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3483,13 +3501,13 @@
         <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>139</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>131</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>20</v>
@@ -3506,14 +3524,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3526,23 +3544,25 @@
         <v>20</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3591,7 +3611,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3603,19 +3623,19 @@
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
@@ -3623,10 +3643,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3637,38 +3657,34 @@
         <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q18" t="s" s="2">
-        <v>195</v>
-      </c>
+      <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
         <v>20</v>
       </c>
@@ -3712,13 +3728,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -3727,16 +3743,16 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -3744,10 +3760,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3758,36 +3774,38 @@
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="P19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q19" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="P19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
         <v>20</v>
       </c>
@@ -3831,13 +3849,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -3846,16 +3864,16 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>20</v>
+        <v>203</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -3863,10 +3881,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3889,19 +3907,19 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3950,7 +3968,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3965,16 +3983,16 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -3982,10 +4000,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3996,7 +4014,7 @@
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4008,19 +4026,19 @@
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4045,13 +4063,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>223</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>224</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4069,13 +4087,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -4084,16 +4102,16 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>147</v>
+        <v>219</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -4101,10 +4119,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4127,19 +4145,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4164,13 +4182,13 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
@@ -4188,7 +4206,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4203,27 +4221,27 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>233</v>
+        <v>147</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4240,25 +4258,25 @@
         <v>20</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4307,7 +4325,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4322,27 +4340,27 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4353,31 +4371,31 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4426,13 +4444,13 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
@@ -4441,16 +4459,16 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>252</v>
+        <v>202</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>20</v>
@@ -4458,10 +4476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4472,7 +4490,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4481,20 +4499,22 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="O25" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4519,13 +4539,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4543,13 +4563,13 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -4558,16 +4578,16 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -4575,10 +4595,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4601,19 +4621,17 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4638,13 +4656,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>20</v>
+        <v>265</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4662,7 +4680,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4677,16 +4695,16 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>197</v>
+        <v>268</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -4694,10 +4712,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4708,7 +4726,7 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4720,19 +4738,19 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4781,13 +4799,13 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
@@ -4796,16 +4814,16 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -4813,10 +4831,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4839,19 +4857,19 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4900,7 +4918,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4912,19 +4930,19 @@
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>287</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -4932,10 +4950,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4946,7 +4964,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4958,16 +4976,20 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="M29" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -5015,25 +5037,25 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AK29" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>197</v>
-      </c>
       <c r="AL29" t="s" s="2">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
@@ -5054,14 +5076,14 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5073,17 +5095,15 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>133</v>
+        <v>295</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5132,22 +5152,22 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>20</v>
@@ -5164,14 +5184,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>299</v>
+        <v>179</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5184,10 +5204,10 @@
         <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>133</v>
@@ -5199,11 +5219,9 @@
         <v>301</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5266,7 +5284,7 @@
         <v>139</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
@@ -5290,7 +5308,7 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5303,23 +5321,25 @@
         <v>20</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>255</v>
+        <v>133</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>306</v>
+        <v>183</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5344,31 +5364,31 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5380,19 +5400,19 @@
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>309</v>
+        <v>131</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>197</v>
+        <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>310</v>
+        <v>20</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5400,10 +5420,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5414,7 +5434,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5426,17 +5446,17 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5461,13 +5481,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>20</v>
+        <v>312</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>20</v>
+        <v>313</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5485,13 +5505,13 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -5500,10 +5520,10 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>205</v>
+        <v>314</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
@@ -5531,7 +5551,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5543,7 +5563,7 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>317</v>
@@ -5551,11 +5571,9 @@
       <c r="M34" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="N34" s="2"/>
+      <c r="O34" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5610,7 +5628,7 @@
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -5619,10 +5637,10 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
@@ -5650,7 +5668,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5662,7 +5680,7 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>322</v>
@@ -5670,9 +5688,11 @@
       <c r="M35" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N35" s="2"/>
+      <c r="N35" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>324</v>
+        <v>218</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5727,7 +5747,7 @@
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
@@ -5736,10 +5756,10 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
@@ -5779,17 +5799,17 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>108</v>
+        <v>251</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>218</v>
+        <v>327</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5814,13 +5834,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>223</v>
+        <v>20</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>224</v>
+        <v>20</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -5853,16 +5873,16 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>147</v>
+        <v>256</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -5870,10 +5890,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5896,17 +5916,17 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>331</v>
+        <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5931,13 +5951,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -5955,7 +5975,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5964,22 +5984,22 @@
         <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>336</v>
+        <v>147</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -5987,10 +6007,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6013,16 +6033,18 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L38" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6070,7 +6092,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6079,22 +6101,22 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>20</v>
+        <v>340</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6116,7 +6138,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6128,20 +6150,16 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>282</v>
+        <v>344</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N39" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="O39" t="s" s="2">
-        <v>347</v>
-      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6195,7 +6213,7 @@
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
@@ -6204,10 +6222,10 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>349</v>
+        <v>202</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
@@ -6221,10 +6239,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6235,7 +6253,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6247,16 +6265,20 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6304,25 +6326,25 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>293</v>
+        <v>348</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>197</v>
+        <v>353</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>20</v>
+        <v>354</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>20</v>
@@ -6336,21 +6358,21 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6362,17 +6384,15 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>133</v>
+        <v>295</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6421,22 +6441,22 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
@@ -6453,14 +6473,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>299</v>
+        <v>179</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6473,10 +6493,10 @@
         <v>20</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>133</v>
@@ -6488,11 +6508,9 @@
         <v>301</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6555,7 +6573,7 @@
         <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>20</v>
@@ -6572,45 +6590,45 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>255</v>
+        <v>133</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>355</v>
+        <v>306</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>356</v>
+        <v>182</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>357</v>
+        <v>183</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6635,13 +6653,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6659,31 +6677,31 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>353</v>
+        <v>307</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>358</v>
+        <v>131</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>359</v>
+        <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>360</v>
+        <v>20</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -6691,10 +6709,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6702,7 +6720,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>88</v>
@@ -6717,19 +6735,19 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -6754,13 +6772,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6778,10 +6796,10 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>88</v>
@@ -6793,16 +6811,16 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -6810,21 +6828,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>370</v>
+        <v>20</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6836,18 +6854,20 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>371</v>
+        <v>195</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -6895,13 +6915,13 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
@@ -6910,16 +6930,16 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>197</v>
+        <v>372</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -6927,21 +6947,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>20</v>
+        <v>375</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -6950,23 +6970,21 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="N46" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>381</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7014,13 +7032,13 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
@@ -7029,16 +7047,16 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>336</v>
+        <v>380</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>382</v>
+        <v>202</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>20</v>
+        <v>381</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7046,10 +7064,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7060,31 +7078,31 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>282</v>
+        <v>336</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7133,13 +7151,13 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
@@ -7148,10 +7166,10 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>388</v>
+        <v>341</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>20</v>
@@ -7165,10 +7183,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7179,28 +7197,32 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>291</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7248,25 +7270,25 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>197</v>
+        <v>393</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>20</v>
@@ -7280,21 +7302,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7306,17 +7328,15 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>133</v>
+        <v>295</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7365,22 +7385,22 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
@@ -7397,14 +7417,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>299</v>
+        <v>179</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7417,10 +7437,10 @@
         <v>20</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>133</v>
@@ -7432,11 +7452,9 @@
         <v>301</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>20</v>
       </c>
@@ -7499,7 +7517,7 @@
         <v>139</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>20</v>
@@ -7516,44 +7534,46 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>393</v>
+        <v>133</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>394</v>
+        <v>305</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>395</v>
+        <v>306</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
       </c>
@@ -7601,31 +7621,31 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>392</v>
+        <v>307</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>197</v>
+        <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>397</v>
+        <v>20</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -7633,10 +7653,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7659,7 +7679,7 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>108</v>
+        <v>398</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>399</v>
@@ -7667,7 +7687,9 @@
       <c r="M52" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N52" s="2"/>
+      <c r="N52" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7692,13 +7714,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>401</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7716,7 +7738,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>88</v>
@@ -7731,18 +7753,133 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AO52" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>20</v>
       </c>
     </row>

--- a/StructureDefinition-ncpi-participant.xlsx
+++ b/StructureDefinition-ncpi-participant.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2015" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="403">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T22:26:51+00:00</t>
+    <t>2026-01-13T18:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -559,26 +559,6 @@
   </si>
   <si>
     <t>Age at Last Vital Status Extension</t>
-  </si>
-  <si>
-    <t>Patient.extension:patientKnowledgeSource</t>
-  </si>
-  <si>
-    <t>patientKnowledgeSource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://nih-ncpi.github.io/ncpi-fhir-ig-2/StructureDefinition/patient-knowledge-source}
-</t>
-  </si>
-  <si>
-    <t>The source of the knowledge represented by this Patient resource.</t>
-  </si>
-  <si>
-    <t>An extension to record the source of the knowledge in a particular
-`Patient` resource.
-The primary use case is to identify those `Patient` resources
-created via inference in order to support indirect pedigree
-relationships.</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -1603,12 +1583,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO53"/>
+  <dimension ref="A1:AO52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.82421875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.83984375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.83984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.5625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.32421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3410,41 +3390,43 @@
         <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C16" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+      <c r="O16" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
       </c>
@@ -3492,7 +3474,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3501,13 +3483,13 @@
         <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>139</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>20</v>
@@ -3524,14 +3506,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3544,25 +3526,23 @@
         <v>20</v>
       </c>
       <c r="I17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J17" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J17" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K17" t="s" s="2">
-        <v>133</v>
+        <v>181</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3611,7 +3591,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3623,19 +3603,19 @@
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
@@ -3643,10 +3623,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3657,84 +3637,88 @@
         <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="O18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="P18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="R18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="P18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q18" s="2"/>
-      <c r="R18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -3743,16 +3727,16 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>193</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -3760,10 +3744,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3774,88 +3758,86 @@
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="O19" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="P19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="P19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="R19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>194</v>
-      </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -3864,16 +3846,16 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>203</v>
+        <v>20</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -3881,10 +3863,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3907,19 +3889,19 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3968,7 +3950,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3983,16 +3965,16 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -4000,10 +3982,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4014,7 +3996,7 @@
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4026,19 +4008,19 @@
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>214</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4063,13 +4045,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>20</v>
+        <v>224</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4087,13 +4069,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -4102,16 +4084,16 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>219</v>
+        <v>147</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -4119,10 +4101,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4145,19 +4127,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>108</v>
+        <v>228</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4182,31 +4164,31 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4221,27 +4203,27 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>147</v>
+        <v>233</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>20</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4258,25 +4240,25 @@
         <v>20</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4325,7 +4307,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4340,27 +4322,27 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4371,31 +4353,31 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4444,13 +4426,13 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
@@ -4459,16 +4441,16 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>202</v>
+        <v>252</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>20</v>
@@ -4476,10 +4458,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4490,7 +4472,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4499,22 +4481,20 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4539,13 +4519,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>20</v>
+        <v>259</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4563,13 +4543,13 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -4578,16 +4558,16 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -4595,10 +4575,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4621,17 +4601,19 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4656,31 +4638,31 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4695,16 +4677,16 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>268</v>
+        <v>197</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -4712,10 +4694,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4726,7 +4708,7 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4738,19 +4720,19 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4799,13 +4781,13 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
@@ -4814,16 +4796,16 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -4831,10 +4813,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4857,19 +4839,19 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4918,7 +4900,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4930,19 +4912,19 @@
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>287</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -4950,10 +4932,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4964,7 +4946,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4976,20 +4958,16 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -5037,25 +5015,25 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>292</v>
+        <v>20</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>293</v>
+        <v>197</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
@@ -5076,14 +5054,14 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5095,15 +5073,17 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M30" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N30" s="2"/>
+      <c r="N30" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5152,22 +5132,22 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>20</v>
@@ -5184,14 +5164,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>179</v>
+        <v>299</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5204,10 +5184,10 @@
         <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>133</v>
@@ -5219,9 +5199,11 @@
         <v>301</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5284,7 +5266,7 @@
         <v>139</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
@@ -5308,7 +5290,7 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>304</v>
+        <v>20</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5321,25 +5303,23 @@
         <v>20</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>133</v>
+        <v>255</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5364,13 +5344,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>20</v>
+        <v>259</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>20</v>
+        <v>307</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>20</v>
+        <v>308</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5388,7 +5368,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5400,19 +5380,19 @@
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>131</v>
+        <v>309</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5420,10 +5400,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5434,7 +5414,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5446,17 +5426,17 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5481,13 +5461,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>312</v>
+        <v>20</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>313</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5505,13 +5485,13 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -5520,10 +5500,10 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>314</v>
+        <v>205</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
@@ -5551,7 +5531,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5563,7 +5543,7 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>317</v>
@@ -5571,9 +5551,11 @@
       <c r="M34" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="N34" s="2"/>
+      <c r="N34" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O34" t="s" s="2">
-        <v>319</v>
+        <v>213</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5628,7 +5610,7 @@
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -5637,10 +5619,10 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
@@ -5668,7 +5650,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5680,7 +5662,7 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>322</v>
@@ -5688,11 +5670,9 @@
       <c r="M35" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5747,7 +5727,7 @@
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
@@ -5756,10 +5736,10 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
@@ -5799,17 +5779,17 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>251</v>
+        <v>108</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5834,13 +5814,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>20</v>
+        <v>224</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -5873,16 +5853,16 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>256</v>
+        <v>147</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -5890,10 +5870,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5916,17 +5896,17 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>108</v>
+        <v>331</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>223</v>
+        <v>332</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5951,13 +5931,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -5975,7 +5955,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5984,22 +5964,22 @@
         <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>20</v>
+        <v>335</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>147</v>
+        <v>336</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -6007,10 +5987,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6033,18 +6013,16 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>339</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6092,7 +6070,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6101,22 +6079,22 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>340</v>
+        <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>342</v>
+        <v>20</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6138,7 +6116,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6150,16 +6128,20 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6213,7 +6195,7 @@
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
@@ -6222,10 +6204,10 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>202</v>
+        <v>349</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
@@ -6239,10 +6221,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6253,7 +6235,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6265,20 +6247,16 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>349</v>
+        <v>291</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6326,25 +6304,25 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>348</v>
+        <v>293</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>353</v>
+        <v>197</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>354</v>
+        <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>20</v>
@@ -6358,21 +6336,21 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6384,15 +6362,17 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N41" s="2"/>
+      <c r="N41" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6441,22 +6421,22 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
@@ -6473,14 +6453,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>179</v>
+        <v>299</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6493,10 +6473,10 @@
         <v>20</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>133</v>
@@ -6508,9 +6488,11 @@
         <v>301</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6573,7 +6555,7 @@
         <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>20</v>
@@ -6590,45 +6572,45 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>304</v>
+        <v>20</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>133</v>
+        <v>255</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>305</v>
+        <v>354</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>306</v>
+        <v>355</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>182</v>
+        <v>356</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>183</v>
+        <v>357</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6653,13 +6635,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6677,31 +6659,31 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>307</v>
+        <v>353</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>131</v>
+        <v>358</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>20</v>
+        <v>359</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>20</v>
+        <v>360</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -6709,10 +6691,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6720,7 +6702,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>88</v>
@@ -6735,19 +6717,19 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -6772,13 +6754,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6796,10 +6778,10 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>88</v>
@@ -6811,16 +6793,16 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -6828,21 +6810,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>20</v>
+        <v>370</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6854,20 +6836,18 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>195</v>
+        <v>371</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -6915,13 +6895,13 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
@@ -6930,16 +6910,16 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>372</v>
+        <v>197</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -6947,21 +6927,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>375</v>
+        <v>20</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -6970,21 +6950,23 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>376</v>
+        <v>331</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7032,13 +7014,13 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
@@ -7047,16 +7029,16 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>380</v>
+        <v>336</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>202</v>
+        <v>382</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7064,10 +7046,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7078,31 +7060,31 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>336</v>
+        <v>282</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7151,13 +7133,13 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
@@ -7166,10 +7148,10 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>341</v>
+        <v>388</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>387</v>
+        <v>197</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>20</v>
@@ -7183,10 +7165,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7197,32 +7179,28 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>389</v>
+        <v>291</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7270,25 +7248,25 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>388</v>
+        <v>293</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>393</v>
+        <v>197</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>20</v>
@@ -7302,21 +7280,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7328,15 +7306,17 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N49" s="2"/>
+      <c r="N49" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7385,22 +7365,22 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
@@ -7417,14 +7397,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>179</v>
+        <v>299</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7437,10 +7417,10 @@
         <v>20</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>133</v>
@@ -7452,9 +7432,11 @@
         <v>301</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
       </c>
@@ -7517,7 +7499,7 @@
         <v>139</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>20</v>
@@ -7534,46 +7516,44 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>304</v>
+        <v>20</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>133</v>
+        <v>393</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>305</v>
+        <v>394</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>306</v>
+        <v>395</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>20</v>
       </c>
@@ -7621,31 +7601,31 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>307</v>
+        <v>392</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>20</v>
+        <v>397</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -7653,10 +7633,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7679,7 +7659,7 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>398</v>
+        <v>108</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>399</v>
@@ -7687,9 +7667,7 @@
       <c r="M52" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N52" t="s" s="2">
-        <v>401</v>
-      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7714,13 +7692,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>20</v>
+        <v>401</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7738,7 +7716,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>88</v>
@@ -7753,133 +7731,18 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>190</v>
+        <v>402</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>402</v>
+        <v>20</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO53" t="s" s="2">
         <v>20</v>
       </c>
     </row>

--- a/StructureDefinition-ncpi-participant.xlsx
+++ b/StructureDefinition-ncpi-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T18:03:13+00:00</t>
+    <t>2026-02-06T18:07:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ncpi-participant.xlsx
+++ b/StructureDefinition-ncpi-participant.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2015" uniqueCount="408">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T18:07:39+00:00</t>
+    <t>2026-03-09T20:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -559,6 +559,26 @@
   </si>
   <si>
     <t>Age at Last Vital Status Extension</t>
+  </si>
+  <si>
+    <t>Patient.extension:patientKnowledgeSource</t>
+  </si>
+  <si>
+    <t>patientKnowledgeSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://nih-ncpi.github.io/ncpi-fhir-ig-2/StructureDefinition/patient-knowledge-source}
+</t>
+  </si>
+  <si>
+    <t>The source of the knowledge represented by this Patient resource.</t>
+  </si>
+  <si>
+    <t>An extension to record the source of the knowledge in a particular
+`Patient` resource.
+The primary use case is to identify those `Patient` resources
+created via inference in order to support indirect pedigree
+relationships.</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -1583,12 +1603,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO52"/>
+  <dimension ref="A1:AO53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="33.83984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="34.82421875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.83984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.32421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="20.5625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3390,43 +3410,41 @@
         <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="O16" t="s" s="2">
-        <v>178</v>
-      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>20</v>
       </c>
@@ -3474,7 +3492,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3483,13 +3501,13 @@
         <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>139</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>131</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>20</v>
@@ -3506,14 +3524,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3526,23 +3544,25 @@
         <v>20</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3591,7 +3611,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3603,19 +3623,19 @@
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
@@ -3623,10 +3643,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3637,38 +3657,34 @@
         <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q18" t="s" s="2">
-        <v>195</v>
-      </c>
+      <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
         <v>20</v>
       </c>
@@ -3712,13 +3728,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -3727,16 +3743,16 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -3744,10 +3760,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3758,36 +3774,38 @@
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="P19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q19" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="P19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
         <v>20</v>
       </c>
@@ -3831,13 +3849,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -3846,16 +3864,16 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>20</v>
+        <v>203</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -3863,10 +3881,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3889,19 +3907,19 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3950,7 +3968,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3965,16 +3983,16 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -3982,10 +4000,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3996,7 +4014,7 @@
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4008,19 +4026,19 @@
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4045,13 +4063,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>223</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>224</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4069,13 +4087,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -4084,16 +4102,16 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>147</v>
+        <v>219</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -4101,10 +4119,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4127,19 +4145,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4164,13 +4182,13 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
@@ -4188,7 +4206,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4203,27 +4221,27 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>233</v>
+        <v>147</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4240,25 +4258,25 @@
         <v>20</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4307,7 +4325,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4322,27 +4340,27 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4353,31 +4371,31 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4426,13 +4444,13 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
@@ -4441,16 +4459,16 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>252</v>
+        <v>202</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>20</v>
@@ -4458,10 +4476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4472,7 +4490,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4481,20 +4499,22 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="O25" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4519,13 +4539,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4543,13 +4563,13 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -4558,16 +4578,16 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -4575,10 +4595,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4601,19 +4621,17 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4638,13 +4656,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>20</v>
+        <v>265</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4662,7 +4680,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4677,16 +4695,16 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>197</v>
+        <v>268</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -4694,10 +4712,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4708,7 +4726,7 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4720,19 +4738,19 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4781,13 +4799,13 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
@@ -4796,16 +4814,16 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -4813,10 +4831,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4839,19 +4857,19 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4900,7 +4918,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4912,19 +4930,19 @@
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>287</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -4932,10 +4950,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4946,7 +4964,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4958,16 +4976,20 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="M29" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -5015,25 +5037,25 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AK29" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>197</v>
-      </c>
       <c r="AL29" t="s" s="2">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
@@ -5054,14 +5076,14 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5073,17 +5095,15 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>133</v>
+        <v>295</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5132,22 +5152,22 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>20</v>
@@ -5164,14 +5184,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>299</v>
+        <v>179</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5184,10 +5204,10 @@
         <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>133</v>
@@ -5199,11 +5219,9 @@
         <v>301</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5266,7 +5284,7 @@
         <v>139</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
@@ -5290,7 +5308,7 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5303,23 +5321,25 @@
         <v>20</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>255</v>
+        <v>133</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>306</v>
+        <v>183</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5344,31 +5364,31 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5380,19 +5400,19 @@
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>309</v>
+        <v>131</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>197</v>
+        <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>310</v>
+        <v>20</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5400,10 +5420,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5414,7 +5434,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5426,17 +5446,17 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5461,13 +5481,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>20</v>
+        <v>312</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>20</v>
+        <v>313</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5485,13 +5505,13 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -5500,10 +5520,10 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>205</v>
+        <v>314</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
@@ -5531,7 +5551,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5543,7 +5563,7 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>317</v>
@@ -5551,11 +5571,9 @@
       <c r="M34" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="N34" s="2"/>
+      <c r="O34" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5610,7 +5628,7 @@
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -5619,10 +5637,10 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
@@ -5650,7 +5668,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5662,7 +5680,7 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>322</v>
@@ -5670,9 +5688,11 @@
       <c r="M35" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N35" s="2"/>
+      <c r="N35" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>324</v>
+        <v>218</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5727,7 +5747,7 @@
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
@@ -5736,10 +5756,10 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
@@ -5779,17 +5799,17 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>108</v>
+        <v>251</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>218</v>
+        <v>327</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5814,13 +5834,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>223</v>
+        <v>20</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>224</v>
+        <v>20</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -5853,16 +5873,16 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>147</v>
+        <v>256</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -5870,10 +5890,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5896,17 +5916,17 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>331</v>
+        <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5931,13 +5951,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -5955,7 +5975,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5964,22 +5984,22 @@
         <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>336</v>
+        <v>147</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -5987,10 +6007,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6013,16 +6033,18 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L38" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6070,7 +6092,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6079,22 +6101,22 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>20</v>
+        <v>340</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6116,7 +6138,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6128,20 +6150,16 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>282</v>
+        <v>344</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N39" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="O39" t="s" s="2">
-        <v>347</v>
-      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6195,7 +6213,7 @@
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
@@ -6204,10 +6222,10 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>349</v>
+        <v>202</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
@@ -6221,10 +6239,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6235,7 +6253,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6247,16 +6265,20 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6304,25 +6326,25 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>293</v>
+        <v>348</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>197</v>
+        <v>353</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>20</v>
+        <v>354</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>20</v>
@@ -6336,21 +6358,21 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6362,17 +6384,15 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>133</v>
+        <v>295</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6421,22 +6441,22 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
@@ -6453,14 +6473,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>299</v>
+        <v>179</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6473,10 +6493,10 @@
         <v>20</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>133</v>
@@ -6488,11 +6508,9 @@
         <v>301</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6555,7 +6573,7 @@
         <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>20</v>
@@ -6572,45 +6590,45 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>255</v>
+        <v>133</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>355</v>
+        <v>306</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>356</v>
+        <v>182</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>357</v>
+        <v>183</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6635,13 +6653,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6659,31 +6677,31 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>353</v>
+        <v>307</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>358</v>
+        <v>131</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>359</v>
+        <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>360</v>
+        <v>20</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -6691,10 +6709,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6702,7 +6720,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>88</v>
@@ -6717,19 +6735,19 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -6754,13 +6772,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6778,10 +6796,10 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>88</v>
@@ -6793,16 +6811,16 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -6810,21 +6828,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>370</v>
+        <v>20</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6836,18 +6854,20 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>371</v>
+        <v>195</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -6895,13 +6915,13 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
@@ -6910,16 +6930,16 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>197</v>
+        <v>372</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -6927,21 +6947,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>20</v>
+        <v>375</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -6950,23 +6970,21 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="N46" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>381</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7014,13 +7032,13 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
@@ -7029,16 +7047,16 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>336</v>
+        <v>380</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>382</v>
+        <v>202</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>20</v>
+        <v>381</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7046,10 +7064,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7060,31 +7078,31 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>282</v>
+        <v>336</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7133,13 +7151,13 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
@@ -7148,10 +7166,10 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>388</v>
+        <v>341</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>197</v>
+        <v>387</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>20</v>
@@ -7165,10 +7183,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7179,28 +7197,32 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>291</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7248,25 +7270,25 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>197</v>
+        <v>393</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>20</v>
@@ -7280,21 +7302,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7306,17 +7328,15 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>133</v>
+        <v>295</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7365,22 +7385,22 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
@@ -7397,14 +7417,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>299</v>
+        <v>179</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7417,10 +7437,10 @@
         <v>20</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>133</v>
@@ -7432,11 +7452,9 @@
         <v>301</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>20</v>
       </c>
@@ -7499,7 +7517,7 @@
         <v>139</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>20</v>
@@ -7516,44 +7534,46 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>393</v>
+        <v>133</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>394</v>
+        <v>305</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>395</v>
+        <v>306</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
       </c>
@@ -7601,31 +7621,31 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>392</v>
+        <v>307</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>197</v>
+        <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>397</v>
+        <v>20</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -7633,10 +7653,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7659,7 +7679,7 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>108</v>
+        <v>398</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>399</v>
@@ -7667,7 +7687,9 @@
       <c r="M52" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N52" s="2"/>
+      <c r="N52" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7692,13 +7714,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>401</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7716,7 +7738,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>88</v>
@@ -7731,18 +7753,133 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AO52" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>20</v>
       </c>
     </row>
